--- a/СВО на 10.09.2026.xlsx
+++ b/СВО на 10.09.2026.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="состоят на учете на 11.09.26" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="состоят на учете на 10.09.26" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="состоят на учете на 13.08.26" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="состоят на учете на 15.07.26" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="состоят на учете на 23.06.26" sheetId="4" state="visible" r:id="rId6"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 07.05.26'!$A$1:$AA$27</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 10.06.26'!$A$1:$AA$27</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 11.09.26'!$A$1:$AA$27</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 10.09.26'!$A$1:$AA$27</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 13.08.26'!$A$1:$AA$27</definedName>
     <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 14.04.26'!$A$1:$AA$27</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 14.05.26'!$A$1:$AA$27</definedName>

--- a/СВО на 10.09.2026.xlsx
+++ b/СВО на 10.09.2026.xlsx
@@ -47,7 +47,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="72">
   <si>
-    <t xml:space="preserve"> На 25.08.2026</t>
+    <t xml:space="preserve"> На 10.09.2026</t>
   </si>
   <si>
     <t xml:space="preserve">состоит на учете</t>
